--- a/downloads/货价监控指标-26.07.29.xlsx
+++ b/downloads/货价监控指标-26.07.29.xlsx
@@ -7559,13 +7559,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1408.52</v>
+        <v>1405.142857142857</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7095958878823162</v>
+        <v>0.7095109800732005</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.894176</v>
+        <v>0.894438</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7575,7 +7575,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.885266</v>
+        <v>0.884556</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7585,7 +7585,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.8283378746594005</v>
+        <v>0.819371727748691</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7595,7 +7595,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.074526339061877</v>
+        <v>0.0762847946804372</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7612,13 +7612,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>116.8</v>
+        <v>116.5357142857143</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2503424657534247</v>
+        <v>0.2516089488201042</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.731436</v>
+        <v>0.734317</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7650,7 +7650,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1481985044187627</v>
+        <v>0.148962148962149</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7667,13 +7667,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>316.12</v>
+        <v>313.9642857142857</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7089712767303556</v>
+        <v>0.7102718689568877</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.882393</v>
+        <v>0.882758</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7683,7 +7683,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.88357</v>
+        <v>0.882866</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7693,7 +7693,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>0.9523809523809524</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7703,7 +7703,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.0477760119292876</v>
+        <v>0.0462958062068844</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7720,13 +7720,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>876.72</v>
+        <v>875.75</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.8070535632813213</v>
+        <v>0.8062477060478773</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.916081</v>
+        <v>0.916198</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7736,7 +7736,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.896254</v>
+        <v>0.89528</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.8054607508532423</v>
+        <v>0.8040540540540541</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7756,7 +7756,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.0891388851887284</v>
+        <v>0.09173719968117811</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1.68</v>
+        <v>1.607142857142857</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.208955223880597</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>96.8</v>
+        <v>96.92857142857143</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.381404958677686</v>
+        <v>0.3817243920412675</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.847162</v>
+        <v>0.855149</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7905,7 +7905,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.789895</v>
+        <v>0.79388</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7925,7 +7925,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0181731229076997</v>
+        <v>0.0215214148732154</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
